--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_coquimbo.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>8.66</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>7.67</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>7.58</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>7.17</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>6.76</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>6.6</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>6.56</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>6.41</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>5.57</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>5.52</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>5.31</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>5.14</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>4.63</v>
       </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>4.48</v>
       </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -577,9 +530,6 @@
       </c>
       <c r="B16">
         <v>3.8</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_coquimbo.xlsx
@@ -385,101 +385,191 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Paiguano</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="B2">
-        <v>8.66</v>
+        <v>7.67</v>
+      </c>
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>-0.3300000000000001</v>
+      </c>
+      <c r="E2">
+        <v>-4.125000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="B3">
-        <v>7.67</v>
+        <v>7.58</v>
+      </c>
+      <c r="C3">
+        <v>5.74</v>
+      </c>
+      <c r="D3">
+        <v>1.84</v>
+      </c>
+      <c r="E3">
+        <v>32.05574912891986</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Ovalle</t>
         </is>
       </c>
       <c r="B4">
-        <v>7.58</v>
+        <v>7.17</v>
+      </c>
+      <c r="C4">
+        <v>7.12</v>
+      </c>
+      <c r="D4">
+        <v>0.04999999999999982</v>
+      </c>
+      <c r="E4">
+        <v>0.7022471910112404</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>Combarbalá</t>
         </is>
       </c>
       <c r="B5">
-        <v>7.17</v>
+        <v>6.76</v>
+      </c>
+      <c r="C5">
+        <v>7.18</v>
+      </c>
+      <c r="D5">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="E5">
+        <v>-5.84958217270195</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="B6">
-        <v>6.76</v>
+        <v>6.6</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="E6">
+        <v>-5.714285714285716</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="B7">
-        <v>6.6</v>
+        <v>6.56</v>
+      </c>
+      <c r="C7">
+        <v>6.79</v>
+      </c>
+      <c r="D7">
+        <v>-0.2300000000000004</v>
+      </c>
+      <c r="E7">
+        <v>-3.387334315169377</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Canela</t>
+          <t>Los Vilos</t>
         </is>
       </c>
       <c r="B8">
-        <v>6.56</v>
+        <v>6.41</v>
+      </c>
+      <c r="C8">
+        <v>6.65</v>
+      </c>
+      <c r="D8">
+        <v>-0.2400000000000002</v>
+      </c>
+      <c r="E8">
+        <v>-3.609022556390984</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="B9">
-        <v>6.41</v>
+        <v>5.57</v>
+      </c>
+      <c r="C9">
+        <v>3.85</v>
+      </c>
+      <c r="D9">
+        <v>1.72</v>
+      </c>
+      <c r="E9">
+        <v>44.67532467532469</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>La Higuera</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="B10">
-        <v>5.57</v>
+        <v>5.52</v>
+      </c>
+      <c r="C10">
+        <v>5.6</v>
+      </c>
+      <c r="D10">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="E10">
+        <v>-1.428571428571435</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B11">
-        <v>5.52</v>
+        <v>5.45</v>
+      </c>
+      <c r="C11">
+        <v>5.69</v>
+      </c>
+      <c r="D11">
+        <v>-0.2400000000000002</v>
+      </c>
+      <c r="E11">
+        <v>-4.217926186291743</v>
       </c>
     </row>
     <row r="12">
@@ -491,6 +581,15 @@
       <c r="B12">
         <v>5.31</v>
       </c>
+      <c r="C12">
+        <v>5.7</v>
+      </c>
+      <c r="D12">
+        <v>-0.3900000000000006</v>
+      </c>
+      <c r="E12">
+        <v>-6.842105263157904</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -501,6 +600,15 @@
       <c r="B13">
         <v>5.14</v>
       </c>
+      <c r="C13">
+        <v>5.41</v>
+      </c>
+      <c r="D13">
+        <v>-0.2700000000000005</v>
+      </c>
+      <c r="E13">
+        <v>-4.990757855822558</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -511,6 +619,15 @@
       <c r="B14">
         <v>4.63</v>
       </c>
+      <c r="C14">
+        <v>5.01</v>
+      </c>
+      <c r="D14">
+        <v>-0.3799999999999999</v>
+      </c>
+      <c r="E14">
+        <v>-7.584830339321358</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -521,6 +638,15 @@
       <c r="B15">
         <v>4.48</v>
       </c>
+      <c r="C15">
+        <v>4.81</v>
+      </c>
+      <c r="D15">
+        <v>-0.3299999999999992</v>
+      </c>
+      <c r="E15">
+        <v>-6.860706860706845</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -530,6 +656,15 @@
       </c>
       <c r="B16">
         <v>3.8</v>
+      </c>
+      <c r="C16">
+        <v>3.44</v>
+      </c>
+      <c r="D16">
+        <v>0.3599999999999999</v>
+      </c>
+      <c r="E16">
+        <v>10.46511627906976</v>
       </c>
     </row>
   </sheetData>
@@ -539,7 +674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -657,50 +792,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paiguano</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="B12">
-        <v>8.66</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="B13">
-        <v>5.52</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="B14">
-        <v>7.58</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="B15">
-        <v>5.31</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Vicuña</t>
-        </is>
-      </c>
-      <c r="B16">
         <v>7.67</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_coquimbo.xlsx
@@ -674,7 +674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -683,11 +683,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -695,138 +690,103 @@
           <t>Andacollo</t>
         </is>
       </c>
-      <c r="B2">
-        <v>3.8</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Canela</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>6.56</v>
+          <t>Los Vilos</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>6.76</v>
+          <t>Canela</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>5.14</v>
+          <t>Ovalle</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Illapel</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>4.63</v>
+          <t>Coquimbo</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>La Higuera</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>5.57</v>
+          <t>La Serena</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>La Serena</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>4.48</v>
+          <t>Combarbalá</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>6.41</v>
+          <t>Punitaqui</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>6.6</v>
+          <t>Paihuano</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ovalle</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>7.17</v>
+          <t>Illapel</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>5.52</v>
+          <t>La Higuera</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>7.58</v>
+          <t>Monte Patria</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Salamanca</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>5.31</v>
+          <t>Río Hurtado</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Vicuña</t>
         </is>
-      </c>
-      <c r="B15">
-        <v>7.67</v>
       </c>
     </row>
   </sheetData>
